--- a/results/gone_abat_jap/figure_data/excel/figure_1_tree_nodes.xlsx
+++ b/results/gone_abat_jap/figure_data/excel/figure_1_tree_nodes.xlsx
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-1621.574988501628</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>-106.1035033325147</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -481,10 +481,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>184.73</v>
+        <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>-110.11</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
         <v>15</v>
@@ -500,10 +500,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-1532.770602848371</v>
+        <v>0.04916356109215105</v>
       </c>
       <c r="C4" t="n">
-        <v>-105.9496674445883</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
@@ -519,10 +519,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-1536.150521532507</v>
+        <v>0.04729238279964155</v>
       </c>
       <c r="C5" t="n">
-        <v>97.76375516952176</v>
+        <v>0.62</v>
       </c>
       <c r="D5" t="n">
         <v>2</v>
@@ -538,10 +538,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-1469.836399805282</v>
+        <v>0.0840049657517785</v>
       </c>
       <c r="C6" t="n">
-        <v>-104.9196674445882</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
         <v>2</v>
@@ -557,10 +557,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-1461.537755350338</v>
+        <v>0.1222923827996416</v>
       </c>
       <c r="C7" t="n">
-        <v>97.34239208373337</v>
+        <v>0.62</v>
       </c>
       <c r="D7" t="n">
         <v>3</v>
@@ -576,10 +576,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-1416.675841423188</v>
+        <v>0.1972923827996416</v>
       </c>
       <c r="C8" t="n">
-        <v>95.54837903697553</v>
+        <v>0.62</v>
       </c>
       <c r="D8" t="n">
         <v>3</v>
@@ -595,10 +595,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-1370.762258993037</v>
+        <v>0.1388540313541657</v>
       </c>
       <c r="C9" t="n">
-        <v>-103.3351451382075</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
         <v>3</v>
@@ -614,10 +614,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-1364.499966273843</v>
+        <v>0.2722923827996416</v>
       </c>
       <c r="C10" t="n">
-        <v>94.10937716817328</v>
+        <v>0.62</v>
       </c>
       <c r="D10" t="n">
         <v>4</v>
@@ -633,10 +633,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-1302.438895819822</v>
+        <v>0.1766789632500195</v>
       </c>
       <c r="C11" t="n">
-        <v>-104.7578439403114</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
         <v>4</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-1305.13309616082</v>
+        <v>0.05000000000000041</v>
       </c>
       <c r="C12" t="n">
-        <v>-285.105677485132</v>
+        <v>-0.62</v>
       </c>
       <c r="D12" t="n">
         <v>5</v>
@@ -671,10 +671,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-1126.4242239178</v>
+        <v>0.2741235659181605</v>
       </c>
       <c r="C13" t="n">
-        <v>-104.1892767057831</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
         <v>5</v>
@@ -690,10 +690,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-1126.4342239178</v>
+        <v>0.1230769230769235</v>
       </c>
       <c r="C14" t="n">
-        <v>-285.609276705783</v>
+        <v>-0.62</v>
       </c>
       <c r="D14" t="n">
         <v>6</v>
@@ -709,10 +709,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-1008.789038363055</v>
+        <v>0.3392483296228358</v>
       </c>
       <c r="C15" t="n">
-        <v>-102.4489702040538</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
         <v>6</v>
@@ -728,10 +728,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-1004.277955886202</v>
+        <v>0.3472923827996416</v>
       </c>
       <c r="C16" t="n">
-        <v>99.15778236538657</v>
+        <v>0.62</v>
       </c>
       <c r="D16" t="n">
         <v>7</v>
@@ -747,10 +747,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-769.9308129924715</v>
+        <v>0.4714841518627567</v>
       </c>
       <c r="C17" t="n">
-        <v>-104.485083241973</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>7</v>
@@ -766,10 +766,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-764.4618954693245</v>
+        <v>0.4745118340969089</v>
       </c>
       <c r="C18" t="n">
-        <v>95.00058685061421</v>
+        <v>0.62</v>
       </c>
       <c r="D18" t="n">
         <v>8</v>
@@ -785,10 +785,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-694.1513806065944</v>
+        <v>0.5134368856858182</v>
       </c>
       <c r="C19" t="n">
-        <v>-105.4741002499973</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
         <v>8</v>
@@ -804,10 +804,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-774.9859644679457</v>
+        <v>0.1961538461538465</v>
       </c>
       <c r="C20" t="n">
-        <v>-250.6581740261258</v>
+        <v>-0.62</v>
       </c>
       <c r="D20" t="n">
         <v>9</v>
@@ -823,10 +823,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-763.9910597662659</v>
+        <v>0.2692307692307696</v>
       </c>
       <c r="C21" t="n">
-        <v>-327.5000869779485</v>
+        <v>-0.62</v>
       </c>
       <c r="D21" t="n">
         <v>9</v>
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-731.4641801072111</v>
+        <v>0.3423076923076926</v>
       </c>
       <c r="C22" t="n">
-        <v>-387.9586871898584</v>
+        <v>-0.62</v>
       </c>
       <c r="D22" t="n">
         <v>9</v>
@@ -861,10 +861,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-687.7213143960776</v>
+        <v>0.4153846153846157</v>
       </c>
       <c r="C23" t="n">
-        <v>-414.8808525941468</v>
+        <v>-0.62</v>
       </c>
       <c r="D23" t="n">
         <v>9</v>
@@ -880,10 +880,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-645.8778094824875</v>
+        <v>0.4884615384615387</v>
       </c>
       <c r="C24" t="n">
-        <v>-362.9514262619589</v>
+        <v>-0.62</v>
       </c>
       <c r="D24" t="n">
         <v>9</v>
@@ -899,10 +899,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-617.3965999160196</v>
+        <v>0.5615384615384618</v>
       </c>
       <c r="C25" t="n">
-        <v>-307.7799625162614</v>
+        <v>-0.62</v>
       </c>
       <c r="D25" t="n">
         <v>9</v>
@@ -918,10 +918,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-567.42</v>
+        <v>0.5835974518212863</v>
       </c>
       <c r="C26" t="n">
-        <v>-106.75</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
         <v>9</v>
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-465.16</v>
+        <v>0.6346153846153848</v>
       </c>
       <c r="C27" t="n">
-        <v>-429.11</v>
+        <v>-0.62</v>
       </c>
       <c r="D27" t="n">
         <v>10</v>
@@ -956,10 +956,10 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-461.74</v>
+        <v>0.6421036291682602</v>
       </c>
       <c r="C28" t="n">
-        <v>-108.3670666145506</v>
+        <v>0</v>
       </c>
       <c r="D28" t="n">
         <v>10</v>
@@ -975,10 +975,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-378.2665329164044</v>
+        <v>0.6883159065051229</v>
       </c>
       <c r="C29" t="n">
-        <v>-107.1641332291011</v>
+        <v>0</v>
       </c>
       <c r="D29" t="n">
         <v>11</v>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-173.42</v>
+        <v>0.8017222992352505</v>
       </c>
       <c r="C30" t="n">
-        <v>-110.11</v>
+        <v>0</v>
       </c>
       <c r="D30" t="n">
         <v>12</v>
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-59.85</v>
+        <v>0.8645965096941438</v>
       </c>
       <c r="C31" t="n">
-        <v>-107.69</v>
+        <v>0</v>
       </c>
       <c r="D31" t="n">
         <v>13</v>
@@ -1032,10 +1032,10 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>63.22977977242164</v>
+        <v>0.9327354898530366</v>
       </c>
       <c r="C32" t="n">
-        <v>-108.1290693821118</v>
+        <v>0</v>
       </c>
       <c r="D32" t="n">
         <v>14</v>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-464.3</v>
+        <v>0.7076923076923078</v>
       </c>
       <c r="C33" t="n">
-        <v>-264.25</v>
+        <v>-0.62</v>
       </c>
       <c r="D33" t="n">
         <v>11</v>
@@ -1070,10 +1070,10 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-385.18</v>
+        <v>0.7807692307692309</v>
       </c>
       <c r="C34" t="n">
-        <v>-315.01</v>
+        <v>-0.62</v>
       </c>
       <c r="D34" t="n">
         <v>12</v>
@@ -1089,10 +1089,10 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-337.4</v>
+        <v>0.8538461538461539</v>
       </c>
       <c r="C35" t="n">
-        <v>-431.46</v>
+        <v>-0.62</v>
       </c>
       <c r="D35" t="n">
         <v>13</v>
@@ -1108,10 +1108,10 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-61.21</v>
+        <v>0.926923076923077</v>
       </c>
       <c r="C36" t="n">
-        <v>-280.67</v>
+        <v>-0.62</v>
       </c>
       <c r="D36" t="n">
         <v>14</v>
@@ -1127,10 +1127,10 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>65.69</v>
+        <v>1</v>
       </c>
       <c r="C37" t="n">
-        <v>-368.75</v>
+        <v>-0.62</v>
       </c>
       <c r="D37" t="n">
         <v>15</v>
